--- a/src/main/resources/PermanentRecordSetup_Field_Values.xlsx
+++ b/src/main/resources/PermanentRecordSetup_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3403A4A-05A3-4398-A29F-8940E8F471A2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81ED8A8-0289-4B76-B4D6-CD41A75E5B4A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="18" activeTab="22" xr2:uid="{A0F3250E-2737-4AB5-82B5-97D4AA917802}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="8" activeTab="8" xr2:uid="{A0F3250E-2737-4AB5-82B5-97D4AA917802}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationFundingSource" sheetId="1" r:id="rId1"/>
@@ -217,9 +217,6 @@
     <t>Non-Construction</t>
   </si>
   <si>
-    <t>Autoamtion Announcement for FDM</t>
-  </si>
-  <si>
     <t>IsMatchRequired__c</t>
   </si>
   <si>
@@ -584,6 +581,9 @@
   </si>
   <si>
     <t>MaxApplicationsAllowed__c</t>
+  </si>
+  <si>
+    <t>Automation Announcement for FDM</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1097,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
         <v>44</v>
@@ -1108,10 +1108,10 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" t="s">
         <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1119,7 +1119,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4">
         <v>20</v>
@@ -1130,7 +1130,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
         <v>35</v>
@@ -1141,7 +1141,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1152,7 +1152,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1163,18 +1163,18 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" t="s">
         <v>70</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
       </c>
       <c r="C9">
         <v>1000</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10">
         <v>10000</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C12">
         <v>10000</v>
@@ -1246,7 +1246,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
         <v>35</v>
@@ -1257,7 +1257,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -1268,7 +1268,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
@@ -1279,7 +1279,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
         <v>35</v>
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
         <v>54</v>
-      </c>
-      <c r="C6" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1301,10 +1301,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1312,7 +1312,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
         <v>35</v>
@@ -1356,7 +1356,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
         <v>35</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
         <v>35</v>
@@ -1378,7 +1378,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
         <v>35</v>
@@ -1414,7 +1414,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
         <v>35</v>
@@ -1425,7 +1425,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -1436,7 +1436,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
@@ -1447,10 +1447,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1458,10 +1458,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
         <v>54</v>
-      </c>
-      <c r="C6" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1469,7 +1469,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
         <v>35</v>
@@ -1480,7 +1480,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
         <v>35</v>
@@ -1524,7 +1524,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
         <v>35</v>
@@ -1535,7 +1535,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
         <v>35</v>
@@ -1546,7 +1546,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
         <v>35</v>
@@ -1586,7 +1586,7 @@
         <v>45</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1642,7 +1642,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
         <v>44</v>
@@ -1653,10 +1653,10 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" t="s">
         <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1664,7 +1664,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4">
         <v>20</v>
@@ -1675,18 +1675,18 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" t="s">
         <v>70</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C7">
         <v>10000</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -1716,10 +1716,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9">
         <v>10000</v>
@@ -1755,7 +1755,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
         <v>35</v>
@@ -1766,7 +1766,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -1777,7 +1777,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
@@ -1788,10 +1788,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1799,10 +1799,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
         <v>54</v>
-      </c>
-      <c r="C6" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1810,7 +1810,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
         <v>35</v>
@@ -1821,7 +1821,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
         <v>35</v>
@@ -1865,7 +1865,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
         <v>35</v>
@@ -1876,7 +1876,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
         <v>35</v>
@@ -1887,7 +1887,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
         <v>35</v>
@@ -1927,7 +1927,7 @@
         <v>45</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1983,7 +1983,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
         <v>44</v>
@@ -1994,10 +1994,10 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" t="s">
         <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2005,7 +2005,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4">
         <v>20</v>
@@ -2016,7 +2016,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5">
         <v>18</v>
@@ -2027,18 +2027,18 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" t="s">
         <v>70</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8">
         <v>10000</v>
@@ -2057,10 +2057,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C10">
         <v>10000</v>
@@ -2107,10 +2107,10 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" t="s">
         <v>80</v>
-      </c>
-      <c r="C2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2118,29 +2118,29 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s">
         <v>82</v>
-      </c>
-      <c r="C3" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" t="s">
         <v>84</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>85</v>
-      </c>
-      <c r="C4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" t="s">
         <v>87</v>
-      </c>
-      <c r="B5" t="s">
-        <v>88</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -2198,10 +2198,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" t="s">
         <v>94</v>
-      </c>
-      <c r="C2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2209,10 +2209,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" t="s">
         <v>96</v>
-      </c>
-      <c r="C3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2220,10 +2220,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" t="s">
         <v>98</v>
-      </c>
-      <c r="C4" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2231,10 +2231,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2242,10 +2242,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2253,10 +2253,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2264,10 +2264,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2275,10 +2275,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -2286,10 +2286,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -2297,10 +2297,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -2308,10 +2308,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2402,7 +2402,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -2413,10 +2413,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" t="s">
         <v>92</v>
-      </c>
-      <c r="C3" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2449,10 +2449,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2460,7 +2460,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
         <v>35</v>
@@ -2471,10 +2471,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2482,7 +2482,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
         <v>35</v>
@@ -2493,7 +2493,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
@@ -2504,7 +2504,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
         <v>35</v>
@@ -2548,10 +2548,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -2559,10 +2559,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -2570,7 +2570,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
         <v>35</v>
@@ -2610,7 +2610,7 @@
         <v>45</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2666,7 +2666,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
         <v>44</v>
@@ -2677,10 +2677,10 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" t="s">
         <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2688,7 +2688,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4">
         <v>20</v>
@@ -2699,10 +2699,10 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2710,7 +2710,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" t="s">
         <v>70</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8">
         <v>10000</v>
@@ -2740,10 +2740,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C10">
         <v>10000</v>
@@ -2788,131 +2788,131 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" t="s">
         <v>132</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>133</v>
-      </c>
-      <c r="C2" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" t="s">
         <v>135</v>
-      </c>
-      <c r="C3" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" t="s">
         <v>137</v>
-      </c>
-      <c r="C4" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" t="s">
         <v>139</v>
-      </c>
-      <c r="C5" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" t="s">
         <v>141</v>
-      </c>
-      <c r="C6" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" t="s">
         <v>143</v>
-      </c>
-      <c r="C7" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" t="s">
         <v>146</v>
-      </c>
-      <c r="C9" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C13" t="s">
         <v>35</v>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C14" t="s">
         <v>35</v>
@@ -2931,21 +2931,21 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" t="s">
         <v>153</v>
-      </c>
-      <c r="C15" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" t="s">
         <v>35</v>
@@ -2953,46 +2953,46 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s">
+        <v>155</v>
+      </c>
+      <c r="C17" t="s">
         <v>156</v>
-      </c>
-      <c r="C17" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C18" t="s">
         <v>158</v>
-      </c>
-      <c r="C18" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B19" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19" t="s">
         <v>160</v>
-      </c>
-      <c r="C19" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B20" t="s">
+        <v>161</v>
+      </c>
+      <c r="C20" t="s">
         <v>162</v>
-      </c>
-      <c r="C20" t="s">
-        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -3026,10 +3026,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -3062,10 +3062,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -3073,10 +3073,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" t="s">
         <v>125</v>
-      </c>
-      <c r="C3" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -3095,7 +3095,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -3106,7 +3106,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C6">
         <v>3650</v>
@@ -3117,10 +3117,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" t="s">
         <v>129</v>
-      </c>
-      <c r="C7" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -3153,10 +3153,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" t="s">
         <v>123</v>
-      </c>
-      <c r="C2" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -3164,10 +3164,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" t="s">
         <v>125</v>
-      </c>
-      <c r="C3" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -3186,7 +3186,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C6">
         <v>3650</v>
@@ -3208,10 +3208,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" t="s">
         <v>129</v>
-      </c>
-      <c r="C7" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -3245,7 +3245,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
         <v>23</v>
@@ -3253,10 +3253,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C3">
         <v>3650</v>
@@ -3293,7 +3293,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
         <v>35</v>
@@ -3304,7 +3304,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -3315,7 +3315,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
@@ -3326,7 +3326,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
         <v>35</v>
@@ -3337,7 +3337,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
@@ -3348,10 +3348,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -3381,7 +3381,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
         <v>35</v>
@@ -3392,7 +3392,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" t="s">
         <v>35</v>
@@ -3403,10 +3403,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -3486,10 +3486,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" t="s">
         <v>108</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -3497,7 +3497,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -3519,7 +3519,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -3530,10 +3530,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" t="s">
         <v>113</v>
-      </c>
-      <c r="C6" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -3552,7 +3552,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
@@ -3563,15 +3563,15 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -3605,10 +3605,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" t="s">
         <v>108</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -3616,7 +3616,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -3627,7 +3627,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -3638,7 +3638,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
         <v>48</v>
@@ -3649,10 +3649,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" t="s">
         <v>113</v>
-      </c>
-      <c r="C6" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -3671,7 +3671,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
@@ -3682,15 +3682,15 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -3724,10 +3724,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -3735,7 +3735,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
         <v>35</v>
@@ -3746,7 +3746,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
@@ -3757,7 +3757,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
         <v>35</v>
@@ -3768,10 +3768,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -3801,7 +3801,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
         <v>35</v>
@@ -3812,7 +3812,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
         <v>35</v>
@@ -3823,10 +3823,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -3870,10 +3870,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" t="s">
         <v>108</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -3881,7 +3881,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -3903,7 +3903,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
         <v>48</v>
@@ -3914,10 +3914,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" t="s">
         <v>113</v>
-      </c>
-      <c r="C6" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -3936,7 +3936,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
@@ -3947,10 +3947,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -3984,7 +3984,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
         <v>35</v>
@@ -3995,7 +3995,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -4006,7 +4006,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
@@ -4017,7 +4017,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
         <v>35</v>
@@ -4028,7 +4028,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
@@ -4039,10 +4039,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -4072,7 +4072,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
         <v>35</v>
@@ -4083,7 +4083,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" t="s">
         <v>35</v>
@@ -4094,10 +4094,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -4142,10 +4142,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" t="s">
         <v>167</v>
-      </c>
-      <c r="C2" t="s">
-        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -4178,10 +4178,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2" t="s">
         <v>169</v>
-      </c>
-      <c r="C2" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -4421,7 +4421,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -4646,7 +4646,7 @@
         <v>45</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>49</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/PermanentRecordSetup_Field_Values.xlsx
+++ b/src/main/resources/PermanentRecordSetup_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductClassic\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3403A4A-05A3-4398-A29F-8940E8F471A2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCE22BD-3115-4DB4-99A4-3C835596EB2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="18" activeTab="22" xr2:uid="{A0F3250E-2737-4AB5-82B5-97D4AA917802}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="4" xr2:uid="{A0F3250E-2737-4AB5-82B5-97D4AA917802}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationFundingSource" sheetId="1" r:id="rId1"/>
@@ -719,9 +719,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -759,7 +759,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -865,7 +865,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1007,7 +1007,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1016,13 +1016,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1DCE2A7-AC21-43E9-8C07-285005A5836C}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1033,7 +1033,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1074,14 +1074,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39E021CB-A850-4212-A4DA-0691E2534CAE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>70</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>70</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>70</v>
       </c>
@@ -1224,13 +1224,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59996C05-0775-48B7-9D95-7CCC6A8555B6}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1241,7 +1241,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1392,13 +1392,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B2966E-302A-41C3-9E0E-A58673655DCC}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1464,7 +1464,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1560,14 +1560,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1EC7B77-96ED-4AEF-A62A-5CDAE9151547}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1619,14 +1619,14 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C0828FE-32F4-44D4-B6A9-8627073BFF05}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1670,7 +1670,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>70</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>70</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>70</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>70</v>
       </c>
@@ -1733,13 +1733,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF260FFC-31A4-4CAF-BD7B-D7015067A8F8}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1901,14 +1901,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5381BA24-0431-49D4-8FE2-4F4D3344249D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1960,14 +1960,14 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F4DDC27-527C-46F2-87A5-15BF0AEB40BE}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>70</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>70</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>70</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>70</v>
       </c>
@@ -2085,13 +2085,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E5964F5-D7FA-4723-932B-BB966F5479B1}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>84</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>87</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>87</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>87</v>
       </c>
@@ -2176,13 +2176,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA88332D-FA22-4263-BBED-F0D1EAC6434D}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2322,13 +2322,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DBD9ECA-358A-4B06-92DD-9626CDEA8E52}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.33203125" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2350,7 +2350,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2361,7 +2361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2380,13 +2380,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8234D517-DFBC-425C-B493-49772C47B8B0}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2427,13 +2427,13 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{472A171D-BB75-41FA-81EA-A70DF5CBF47A}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2466,7 +2466,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2565,7 +2565,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2584,14 +2584,14 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{710D0B2F-8F9B-487D-B96E-76C272E8E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2643,14 +2643,14 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB919764-9A5C-4A4C-85EB-9571B28F299A}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>70</v>
       </c>
@@ -2727,7 +2727,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>70</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>70</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>70</v>
       </c>
@@ -2768,14 +2768,14 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E3A078-0D1D-48D3-B393-911B6241D28F}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>132</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>132</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>132</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>132</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>132</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>132</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>132</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>132</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>132</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>132</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>132</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>132</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>132</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>132</v>
       </c>
@@ -2940,7 +2940,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>132</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>132</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>132</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>132</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>132</v>
       </c>
@@ -3003,14 +3003,14 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B32FD7BE-F529-42B4-BDF1-783BA1DBC83B}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3040,13 +3040,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{840BF598-57FF-46EE-BE91-5A3335FAF129}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3131,13 +3131,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{412ADA1A-E02A-469C-8613-6D09F7DDD1D5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3203,7 +3203,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3222,14 +3222,14 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E304CFBD-71A2-46A1-A012-E32225A79282}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3240,7 +3240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>84</v>
       </c>
@@ -3270,14 +3270,14 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AF21BB0-930C-4861-B6C0-731A6F5E609D}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" customWidth="1"/>
-    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3321,7 +3321,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -3398,7 +3398,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -3428,13 +3428,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B09538CD-9B94-4737-8F41-95B4C84D9AFE}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -3464,13 +3464,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FE628C-0DE3-4901-8582-749A941E5CA7}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="38.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" customWidth="1"/>
+    <col min="3" max="3" width="38.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -3569,7 +3569,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G19" t="s">
         <v>117</v>
       </c>
@@ -3583,13 +3583,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D25C9C3-7D25-485E-9750-08B5F6645995}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="38.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" customWidth="1"/>
+    <col min="3" max="3" width="38.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -3688,7 +3688,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G19" t="s">
         <v>117</v>
       </c>
@@ -3701,14 +3701,14 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{093FA22C-2C74-4511-B68B-31D1371E4C83}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" customWidth="1"/>
-    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3719,7 +3719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3741,7 +3741,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3785,7 +3785,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -3848,13 +3848,13 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98839D49-A13C-467E-B794-4DB887B342F2}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="38.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" customWidth="1"/>
+    <col min="3" max="3" width="38.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3931,7 +3931,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -3961,14 +3961,14 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3E315DE-948D-4F7E-8DEB-F72EC13ECB5D}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" customWidth="1"/>
-    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3979,7 +3979,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3990,7 +3990,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -4001,7 +4001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4012,7 +4012,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -4089,7 +4089,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -4100,7 +4100,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -4119,14 +4119,14 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE98B419-FC74-466A-B696-3CD64016B12D}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" customWidth="1"/>
-    <col min="3" max="3" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="34.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4156,13 +4156,13 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03367B2B-715C-4659-A6C4-721231659FD4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4214,13 +4214,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{506C7784-46A1-4098-9646-BE6C85090D64}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.5546875" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -4242,7 +4242,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -4253,7 +4253,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -4275,7 +4275,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -4305,13 +4305,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC09E43-DFF8-4817-8CA1-1F727E26DEC6}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4355,7 +4355,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -4366,7 +4366,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -4385,13 +4385,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{347FF807-1516-41B4-935D-682146391E36}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4402,7 +4402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4413,7 +4413,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -4424,7 +4424,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -4465,13 +4465,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31BCE2D0-C669-4A3E-994D-167DE891C4AB}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4482,7 +4482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -4504,7 +4504,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -4559,13 +4559,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BDE6362-8D33-46B9-98EC-00CCD3A19C59}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -4620,14 +4620,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36BD1AFD-A816-4C84-A455-35E729746BE0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
